--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_SAN ANTONIO CÁCERES.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_SAN ANTONIO CÁCERES.xlsx
@@ -565,13 +565,13 @@
         <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>118.977</v>
+        <v>129.5402</v>
       </c>
       <c r="E2" t="n">
-        <v>120.2431</v>
+        <v>128.8894</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.2658</v>
+        <v>0.6510000000000002</v>
       </c>
       <c r="G2" t="n">
         <v>97.866</v>
@@ -610,13 +610,13 @@
         <v>67.62990000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>-14.933</v>
+        <v>-4.3696</v>
       </c>
       <c r="T2" t="n">
-        <v>-12.4049</v>
+        <v>-3.7585</v>
       </c>
       <c r="U2" t="n">
-        <v>-2.5279</v>
+        <v>-0.6113999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>41.7879</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. MAIGA</t>
+          <t>J. NDJUNGU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>50.2193</v>
+        <v>35.7327</v>
       </c>
       <c r="E3" t="n">
-        <v>62.777</v>
+        <v>28.4548</v>
       </c>
       <c r="F3" t="n">
-        <v>-12.5576</v>
+        <v>7.2783</v>
       </c>
       <c r="G3" t="n">
-        <v>14.575</v>
+        <v>23.5103</v>
       </c>
       <c r="H3" t="n">
-        <v>11.8943</v>
+        <v>1.5289</v>
       </c>
       <c r="I3" t="n">
-        <v>2.6806</v>
+        <v>21.9815</v>
       </c>
       <c r="J3" t="n">
-        <v>58.7968</v>
+        <v>41.6214</v>
       </c>
       <c r="K3" t="n">
-        <v>46.5981</v>
+        <v>22.2536</v>
       </c>
       <c r="L3" t="n">
-        <v>12.1988</v>
+        <v>19.3677</v>
       </c>
       <c r="M3" t="n">
-        <v>-44.2218</v>
+        <v>-18.1111</v>
       </c>
       <c r="N3" t="n">
-        <v>-34.7035</v>
+        <v>-20.7249</v>
       </c>
       <c r="O3" t="n">
-        <v>-9.5183</v>
+        <v>2.6138</v>
       </c>
       <c r="P3" t="n">
-        <v>14.6376</v>
+        <v>-7.041</v>
       </c>
       <c r="Q3" t="n">
-        <v>-40.3925</v>
+        <v>-39.6513</v>
       </c>
       <c r="R3" t="n">
-        <v>55.0301</v>
+        <v>32.6104</v>
       </c>
       <c r="S3" t="n">
-        <v>22.0162</v>
+        <v>5.2921</v>
       </c>
       <c r="T3" t="n">
-        <v>25.1835</v>
+        <v>1.3132</v>
       </c>
       <c r="U3" t="n">
-        <v>-3.1673</v>
+        <v>3.9792</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.0098</v>
+        <v>13.9714</v>
       </c>
       <c r="W3" t="n">
-        <v>19.189</v>
+        <v>25.1716</v>
       </c>
       <c r="X3" t="n">
-        <v>-20.199</v>
+        <v>-11.2003</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. NDJUNGU</t>
+          <t>G. MAIGA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>42.0364</v>
+        <v>35.5675</v>
       </c>
       <c r="E4" t="n">
-        <v>31.1074</v>
+        <v>44.5246</v>
       </c>
       <c r="F4" t="n">
-        <v>10.929</v>
+        <v>-8.9572</v>
       </c>
       <c r="G4" t="n">
-        <v>23.5103</v>
+        <v>14.575</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5289</v>
+        <v>11.8943</v>
       </c>
       <c r="I4" t="n">
-        <v>21.9815</v>
+        <v>2.6806</v>
       </c>
       <c r="J4" t="n">
-        <v>41.6214</v>
+        <v>58.7968</v>
       </c>
       <c r="K4" t="n">
-        <v>22.2536</v>
+        <v>46.5981</v>
       </c>
       <c r="L4" t="n">
-        <v>19.3677</v>
+        <v>12.1988</v>
       </c>
       <c r="M4" t="n">
-        <v>-18.1111</v>
+        <v>-44.2218</v>
       </c>
       <c r="N4" t="n">
-        <v>-20.7249</v>
+        <v>-34.7035</v>
       </c>
       <c r="O4" t="n">
-        <v>2.6138</v>
+        <v>-9.5183</v>
       </c>
       <c r="P4" t="n">
-        <v>-7.041</v>
+        <v>14.6376</v>
       </c>
       <c r="Q4" t="n">
-        <v>-39.6513</v>
+        <v>-40.3925</v>
       </c>
       <c r="R4" t="n">
-        <v>32.6104</v>
+        <v>55.0301</v>
       </c>
       <c r="S4" t="n">
-        <v>11.5957</v>
+        <v>7.3646</v>
       </c>
       <c r="T4" t="n">
-        <v>3.9661</v>
+        <v>6.9313</v>
       </c>
       <c r="U4" t="n">
-        <v>7.6297</v>
+        <v>0.4335000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>13.9714</v>
+        <v>-1.0098</v>
       </c>
       <c r="W4" t="n">
-        <v>25.1716</v>
+        <v>19.189</v>
       </c>
       <c r="X4" t="n">
-        <v>-11.2003</v>
+        <v>-20.199</v>
       </c>
     </row>
     <row r="5">
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. LOPEZ CALZADA</t>
+          <t>L. DALLACOSTA ORTIZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D7" t="n">
-        <v>10.6005</v>
+        <v>10.9278</v>
       </c>
       <c r="E7" t="n">
-        <v>13.6714</v>
+        <v>15.9552</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.071</v>
+        <v>-5.027200000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>23.6356</v>
+        <v>7.982000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>10.9126</v>
+        <v>-12.9162</v>
       </c>
       <c r="I7" t="n">
-        <v>12.7227</v>
+        <v>20.8978</v>
       </c>
       <c r="J7" t="n">
-        <v>55.9391</v>
+        <v>35.3982</v>
       </c>
       <c r="K7" t="n">
-        <v>35.4028</v>
+        <v>10.7943</v>
       </c>
       <c r="L7" t="n">
-        <v>20.5363</v>
+        <v>24.604</v>
       </c>
       <c r="M7" t="n">
-        <v>-32.3037</v>
+        <v>-27.4165</v>
       </c>
       <c r="N7" t="n">
-        <v>-24.4904</v>
+        <v>-23.7101</v>
       </c>
       <c r="O7" t="n">
-        <v>-7.813099999999999</v>
+        <v>-3.7062</v>
       </c>
       <c r="P7" t="n">
-        <v>-31.6838</v>
+        <v>0.9263000000000002</v>
       </c>
       <c r="Q7" t="n">
-        <v>-81.34100000000001</v>
+        <v>-37.9835</v>
       </c>
       <c r="R7" t="n">
-        <v>49.6569</v>
+        <v>38.9104</v>
       </c>
       <c r="S7" t="n">
-        <v>6.123200000000001</v>
+        <v>-4.2702</v>
       </c>
       <c r="T7" t="n">
-        <v>3.2039</v>
+        <v>-4.425</v>
       </c>
       <c r="U7" t="n">
-        <v>2.9194</v>
+        <v>0.1550000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>12.5259</v>
+        <v>6.289700000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>35.8691</v>
+        <v>22.9656</v>
       </c>
       <c r="X7" t="n">
-        <v>-23.3437</v>
+        <v>-16.6759</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. VALVERDE PIZARRO</t>
+          <t>L. LOPEZ CALZADA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>7.4451</v>
+        <v>7.7142</v>
       </c>
       <c r="E8" t="n">
-        <v>8.183</v>
+        <v>11.0329</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7383000000000006</v>
+        <v>-3.3187</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0546</v>
+        <v>23.6356</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4669999999999999</v>
+        <v>10.9126</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5878</v>
+        <v>12.7227</v>
       </c>
       <c r="J8" t="n">
-        <v>7.0146</v>
+        <v>55.9391</v>
       </c>
       <c r="K8" t="n">
-        <v>5.199400000000001</v>
+        <v>35.4028</v>
       </c>
       <c r="L8" t="n">
-        <v>1.8153</v>
+        <v>20.5363</v>
       </c>
       <c r="M8" t="n">
-        <v>-8.0693</v>
+        <v>-32.3037</v>
       </c>
       <c r="N8" t="n">
-        <v>-5.6665</v>
+        <v>-24.4904</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.4029</v>
+        <v>-7.813099999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>5.0028</v>
+        <v>-31.6838</v>
       </c>
       <c r="Q8" t="n">
-        <v>-6.6703</v>
+        <v>-81.34100000000001</v>
       </c>
       <c r="R8" t="n">
-        <v>11.6731</v>
+        <v>49.6569</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2929</v>
+        <v>3.2367</v>
       </c>
       <c r="T8" t="n">
-        <v>1.8618</v>
+        <v>0.5654</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5686000000000001</v>
+        <v>2.6717</v>
       </c>
       <c r="V8" t="n">
-        <v>2.2037</v>
+        <v>12.5259</v>
       </c>
       <c r="W8" t="n">
-        <v>5.977</v>
+        <v>35.8691</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.7733</v>
+        <v>-23.3437</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. GONZÁLEZ ROSCO</t>
+          <t>J. VALVERDE PIZARRO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D9" t="n">
-        <v>4.1208</v>
+        <v>5.0506</v>
       </c>
       <c r="E9" t="n">
-        <v>4.1208</v>
+        <v>6.290799999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>-1.2403</v>
       </c>
       <c r="G9" t="n">
-        <v>4.1208</v>
+        <v>-1.0546</v>
       </c>
       <c r="H9" t="n">
-        <v>2.2546</v>
+        <v>-0.4669999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>1.8662</v>
+        <v>-0.5878</v>
       </c>
       <c r="J9" t="n">
-        <v>4.1208</v>
+        <v>7.0146</v>
       </c>
       <c r="K9" t="n">
-        <v>2.2546</v>
+        <v>5.199400000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>1.8662</v>
+        <v>1.8153</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-8.0693</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-5.6665</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-2.4029</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>5.0028</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-6.6703</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>11.6731</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-1.1015</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-0.03069999999999995</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-1.0709</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>2.2037</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>5.977</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-3.7733</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. MARTÍNEZ AGUDO</t>
+          <t>F. GONZÁLEZ ROSCO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,34 +1186,34 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>4.0767</v>
+        <v>4.1208</v>
       </c>
       <c r="E10" t="n">
-        <v>4.0767</v>
+        <v>4.1208</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>4.0767</v>
+        <v>4.1208</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9662999999999999</v>
+        <v>2.2546</v>
       </c>
       <c r="I10" t="n">
-        <v>3.1105</v>
+        <v>1.8662</v>
       </c>
       <c r="J10" t="n">
-        <v>4.0767</v>
+        <v>4.1208</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9662999999999999</v>
+        <v>2.2546</v>
       </c>
       <c r="L10" t="n">
-        <v>3.1105</v>
+        <v>1.8662</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L. DALLACOSTA ORTIZ</t>
+          <t>A. MARTÍNEZ AGUDO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>2.8543</v>
+        <v>4.0767</v>
       </c>
       <c r="E11" t="n">
-        <v>10.477</v>
+        <v>4.0767</v>
       </c>
       <c r="F11" t="n">
-        <v>-7.6227</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>7.982000000000001</v>
+        <v>4.0767</v>
       </c>
       <c r="H11" t="n">
-        <v>-12.9162</v>
+        <v>0.9662999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>20.8978</v>
+        <v>3.1105</v>
       </c>
       <c r="J11" t="n">
-        <v>35.3982</v>
+        <v>4.0767</v>
       </c>
       <c r="K11" t="n">
-        <v>10.7943</v>
+        <v>0.9662999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>24.604</v>
+        <v>3.1105</v>
       </c>
       <c r="M11" t="n">
-        <v>-27.4165</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-23.7101</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>-3.7062</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9263000000000002</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-37.9835</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>38.9104</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-12.3442</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>-9.902899999999999</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.4405</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>6.289700000000001</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>22.9656</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-16.6759</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F. MARQUEZ CORTES</t>
+          <t>V. TOBOSO PANIAGUA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.6147</v>
+        <v>-0.3216</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0547</v>
+        <v>-0.2731</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.0484</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.4294</v>
+        <v>0.1811</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4294</v>
+        <v>-0.09700000000000009</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>0.278</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.4708</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>-0.2449</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>0.7157</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4294</v>
+        <v>-0.2897000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4294</v>
+        <v>0.148</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>-0.4377</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>0.1853</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.1117</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1853</v>
+        <v>0.2559</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0547</v>
+        <v>0.1825</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1306</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-0.9439</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.9439</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V. TOBOSO PANIAGUA</t>
+          <t>F. MARQUEZ CORTES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.1669</v>
+        <v>-0.6147</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.8723</v>
+        <v>-0.0547</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2948</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1811</v>
+        <v>-0.4294</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.09700000000000009</v>
+        <v>-0.4294</v>
       </c>
       <c r="I15" t="n">
-        <v>0.278</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4708</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.2449</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7157</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2897000000000001</v>
+        <v>-0.4294</v>
       </c>
       <c r="N15" t="n">
-        <v>0.148</v>
+        <v>-0.4294</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4377</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1853</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1117</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5894999999999999</v>
+        <v>-0.1853</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4165</v>
+        <v>-0.0547</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1729</v>
+        <v>-0.1306</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.9439</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.9439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.2738</v>
+        <v>-2.1513</v>
       </c>
       <c r="E16" t="n">
-        <v>0.01870000000000005</v>
+        <v>0.1167000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.2926</v>
+        <v>-2.268</v>
       </c>
       <c r="G16" t="n">
         <v>-1.1785</v>
@@ -1702,13 +1702,13 @@
         <v>0.3706</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.4658</v>
+        <v>-1.3433</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7113</v>
+        <v>-0.6133999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7546999999999999</v>
+        <v>-0.73</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. ARIAS HERNANDEZ</t>
+          <t>F. BRAVO FUENTENEBRO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.0441</v>
+        <v>-2.7097</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.8734</v>
+        <v>-3.4321</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1707</v>
+        <v>0.7224</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.1891</v>
+        <v>-2.3691</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.7514</v>
+        <v>1.4125</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4377</v>
+        <v>-3.7817</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.2843</v>
+        <v>-1.7585</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.2843</v>
+        <v>0.6871</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-2.4456</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9048</v>
+        <v>-0.6107</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4671</v>
+        <v>0.7255</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4377</v>
+        <v>-1.3361</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3706</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3706</v>
+        <v>1.6676</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.91</v>
+        <v>-0.4698</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2736</v>
+        <v>-0.1352</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6364</v>
+        <v>-0.3345</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3155</v>
+        <v>0.3144</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3155</v>
+        <v>0.3144</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. BRAVO FUENTENEBRO</t>
+          <t>B. ARIAS HERNANDEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.8138</v>
+        <v>-2.8236</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.1176</v>
+        <v>-1.6775</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3038</v>
+        <v>-1.1461</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.3691</v>
+        <v>-2.1891</v>
       </c>
       <c r="H18" t="n">
-        <v>1.4125</v>
+        <v>-1.7514</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.7817</v>
+        <v>-0.4377</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.7585</v>
+        <v>-1.2843</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6871</v>
+        <v>-1.2843</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.4456</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6107</v>
+        <v>-0.9048</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7255</v>
+        <v>-0.4671</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.3361</v>
+        <v>-0.4377</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1853</v>
+        <v>0.3706</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6676</v>
+        <v>0.3706</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.5738</v>
+        <v>-0.6895</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8207</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7531</v>
+        <v>-0.6118</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3144</v>
+        <v>-0.3155</v>
       </c>
       <c r="W18" t="n">
-        <v>0.3144</v>
+        <v>-0.3155</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>-8.382</v>
+        <v>-8.042400000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>-7.2835</v>
+        <v>-7.37</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0985</v>
+        <v>-0.6724999999999998</v>
       </c>
       <c r="G19" t="n">
         <v>-5.7649</v>
@@ -1936,13 +1936,13 @@
         <v>5.3735</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.8623</v>
+        <v>-1.5228</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4824</v>
+        <v>-0.5688</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.3798</v>
+        <v>-0.9537999999999999</v>
       </c>
       <c r="V19" t="n">
         <v>-4.09</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. CABALLERO CARPIO</t>
+          <t>A. USAOLA REDONDO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,76 +1966,76 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D20" t="n">
-        <v>-10.4688</v>
+        <v>-9.075200000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>-8.182</v>
+        <v>-9.866099999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.2865</v>
+        <v>0.7907000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>-15.5871</v>
+        <v>-13.818</v>
       </c>
       <c r="H20" t="n">
-        <v>-13.1379</v>
+        <v>-12.598</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.4489</v>
+        <v>-1.2201</v>
       </c>
       <c r="J20" t="n">
-        <v>-5.6851</v>
+        <v>-5.2213</v>
       </c>
       <c r="K20" t="n">
-        <v>-6.2763</v>
+        <v>-4.0997</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5911999999999999</v>
+        <v>-1.1217</v>
       </c>
       <c r="M20" t="n">
-        <v>-9.901900000000001</v>
+        <v>-8.5969</v>
       </c>
       <c r="N20" t="n">
-        <v>-6.8618</v>
+        <v>-8.4983</v>
       </c>
       <c r="O20" t="n">
-        <v>-3.0401</v>
+        <v>-0.09869999999999998</v>
       </c>
       <c r="P20" t="n">
-        <v>2.9646</v>
+        <v>-0.5559999999999996</v>
       </c>
       <c r="Q20" t="n">
-        <v>-9.264099999999999</v>
+        <v>-18.714</v>
       </c>
       <c r="R20" t="n">
-        <v>12.229</v>
+        <v>18.1581</v>
       </c>
       <c r="S20" t="n">
-        <v>4.3565</v>
+        <v>-3.1999</v>
       </c>
       <c r="T20" t="n">
-        <v>4.2505</v>
+        <v>-1.6653</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1056</v>
+        <v>-1.5344</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.2028</v>
+        <v>8.498699999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>2.5165</v>
+        <v>15.7346</v>
       </c>
       <c r="X20" t="n">
-        <v>-4.7195</v>
+        <v>-7.2358</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. USAOLA REDONDO</t>
+          <t>S. CABALLERO CARPIO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2044,76 +2044,76 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D21" t="n">
-        <v>-14.2823</v>
+        <v>-14.5157</v>
       </c>
       <c r="E21" t="n">
-        <v>-12.9162</v>
+        <v>-11.1604</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3664</v>
+        <v>-3.3552</v>
       </c>
       <c r="G21" t="n">
-        <v>-13.818</v>
+        <v>-15.5871</v>
       </c>
       <c r="H21" t="n">
-        <v>-12.598</v>
+        <v>-13.1379</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.2201</v>
+        <v>-2.4489</v>
       </c>
       <c r="J21" t="n">
-        <v>-5.2213</v>
+        <v>-5.6851</v>
       </c>
       <c r="K21" t="n">
-        <v>-4.0997</v>
+        <v>-6.2763</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.1217</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>-8.5969</v>
+        <v>-9.901900000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>-8.4983</v>
+        <v>-6.8618</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.09869999999999998</v>
+        <v>-3.0401</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.5559999999999996</v>
+        <v>2.9646</v>
       </c>
       <c r="Q21" t="n">
-        <v>-18.714</v>
+        <v>-9.264099999999999</v>
       </c>
       <c r="R21" t="n">
-        <v>18.1581</v>
+        <v>12.229</v>
       </c>
       <c r="S21" t="n">
-        <v>-8.407</v>
+        <v>0.3094999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-4.7151</v>
+        <v>1.2722</v>
       </c>
       <c r="U21" t="n">
-        <v>-3.6917</v>
+        <v>-0.9627</v>
       </c>
       <c r="V21" t="n">
-        <v>8.498699999999999</v>
+        <v>-2.2028</v>
       </c>
       <c r="W21" t="n">
-        <v>15.7346</v>
+        <v>2.5165</v>
       </c>
       <c r="X21" t="n">
-        <v>-7.2358</v>
+        <v>-4.7195</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. MARTINEZ AGUDO</t>
+          <t>J. LOPEZ YUSTE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2122,76 +2122,76 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D22" t="n">
-        <v>-25.3753</v>
+        <v>-18.0027</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.774800000000003</v>
+        <v>-4.6448</v>
       </c>
       <c r="F22" t="n">
-        <v>-17.6008</v>
+        <v>-13.3577</v>
       </c>
       <c r="G22" t="n">
-        <v>-31.7111</v>
+        <v>-20.0839</v>
       </c>
       <c r="H22" t="n">
-        <v>-24.5837</v>
+        <v>-21.3558</v>
       </c>
       <c r="I22" t="n">
-        <v>-7.127300000000002</v>
+        <v>1.2721</v>
       </c>
       <c r="J22" t="n">
-        <v>1.912199999999999</v>
+        <v>23.9704</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.6779</v>
+        <v>14.4014</v>
       </c>
       <c r="L22" t="n">
-        <v>4.5901</v>
+        <v>9.568999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-33.6231</v>
+        <v>-44.0541</v>
       </c>
       <c r="N22" t="n">
-        <v>-21.9059</v>
+        <v>-35.7572</v>
       </c>
       <c r="O22" t="n">
-        <v>-11.7171</v>
+        <v>-8.297000000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>17.2318</v>
+        <v>7.5967</v>
       </c>
       <c r="Q22" t="n">
-        <v>-14.6376</v>
+        <v>-48.1743</v>
       </c>
       <c r="R22" t="n">
-        <v>31.8693</v>
+        <v>55.7712</v>
       </c>
       <c r="S22" t="n">
-        <v>-4.414099999999999</v>
+        <v>-3.7568</v>
       </c>
       <c r="T22" t="n">
-        <v>-2.6</v>
+        <v>-4.0398</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.8141</v>
+        <v>0.2824999999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>-6.4819</v>
+        <v>-1.7587</v>
       </c>
       <c r="W22" t="n">
-        <v>7.5509</v>
+        <v>23.5995</v>
       </c>
       <c r="X22" t="n">
-        <v>-14.0328</v>
+        <v>-25.3581</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>F. GONZALEZ ROSCO</t>
+          <t>A. MARTINEZ AGUDO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2200,76 +2200,76 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D23" t="n">
-        <v>-34.391</v>
+        <v>-22.2327</v>
       </c>
       <c r="E23" t="n">
-        <v>-20.7979</v>
+        <v>-5.464700000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-13.593</v>
+        <v>-16.7679</v>
       </c>
       <c r="G23" t="n">
-        <v>-22.9424</v>
+        <v>-31.7111</v>
       </c>
       <c r="H23" t="n">
-        <v>-14.8902</v>
+        <v>-24.5837</v>
       </c>
       <c r="I23" t="n">
-        <v>-8.0524</v>
+        <v>-7.127300000000002</v>
       </c>
       <c r="J23" t="n">
-        <v>-7.1078</v>
+        <v>1.912199999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.0534</v>
+        <v>-2.6779</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.0546</v>
+        <v>4.5901</v>
       </c>
       <c r="M23" t="n">
-        <v>-15.8347</v>
+        <v>-33.6231</v>
       </c>
       <c r="N23" t="n">
-        <v>-10.8367</v>
+        <v>-21.9059</v>
       </c>
       <c r="O23" t="n">
-        <v>-4.998</v>
+        <v>-11.7171</v>
       </c>
       <c r="P23" t="n">
-        <v>7.4116</v>
+        <v>17.2318</v>
       </c>
       <c r="Q23" t="n">
-        <v>-12.2287</v>
+        <v>-14.6376</v>
       </c>
       <c r="R23" t="n">
-        <v>19.6404</v>
+        <v>31.8693</v>
       </c>
       <c r="S23" t="n">
-        <v>-4.1958</v>
+        <v>-1.2713</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.7743</v>
+        <v>-0.29</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.4215</v>
+        <v>-0.9812</v>
       </c>
       <c r="V23" t="n">
-        <v>-14.6639</v>
+        <v>-6.4819</v>
       </c>
       <c r="W23" t="n">
-        <v>0.3133</v>
+        <v>7.5509</v>
       </c>
       <c r="X23" t="n">
-        <v>-14.9773</v>
+        <v>-14.0328</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. LOPEZ YUSTE</t>
+          <t>F. GONZALEZ ROSCO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2278,70 +2278,70 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D24" t="n">
-        <v>-35.3795</v>
+        <v>-31.1447</v>
       </c>
       <c r="E24" t="n">
-        <v>-19.167</v>
+        <v>-19.6745</v>
       </c>
       <c r="F24" t="n">
-        <v>-16.2125</v>
+        <v>-11.4704</v>
       </c>
       <c r="G24" t="n">
-        <v>-20.0839</v>
+        <v>-22.9424</v>
       </c>
       <c r="H24" t="n">
-        <v>-21.3558</v>
+        <v>-14.8902</v>
       </c>
       <c r="I24" t="n">
-        <v>1.2721</v>
+        <v>-8.0524</v>
       </c>
       <c r="J24" t="n">
-        <v>23.9704</v>
+        <v>-7.1078</v>
       </c>
       <c r="K24" t="n">
-        <v>14.4014</v>
+        <v>-4.0534</v>
       </c>
       <c r="L24" t="n">
-        <v>9.568999999999999</v>
+        <v>-3.0546</v>
       </c>
       <c r="M24" t="n">
-        <v>-44.0541</v>
+        <v>-15.8347</v>
       </c>
       <c r="N24" t="n">
-        <v>-35.7572</v>
+        <v>-10.8367</v>
       </c>
       <c r="O24" t="n">
-        <v>-8.297000000000001</v>
+        <v>-4.998</v>
       </c>
       <c r="P24" t="n">
-        <v>7.5967</v>
+        <v>7.4116</v>
       </c>
       <c r="Q24" t="n">
-        <v>-48.1743</v>
+        <v>-12.2287</v>
       </c>
       <c r="R24" t="n">
-        <v>55.7712</v>
+        <v>19.6404</v>
       </c>
       <c r="S24" t="n">
-        <v>-21.1336</v>
+        <v>-0.9498999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-18.5616</v>
+        <v>-0.6510999999999998</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.571899999999999</v>
+        <v>-0.2985</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.7587</v>
+        <v>-14.6639</v>
       </c>
       <c r="W24" t="n">
-        <v>23.5995</v>
+        <v>0.3133</v>
       </c>
       <c r="X24" t="n">
-        <v>-25.3581</v>
+        <v>-14.9773</v>
       </c>
     </row>
     <row r="25">
@@ -2359,25 +2359,25 @@
         <v>26</v>
       </c>
       <c r="D25" t="n">
-        <v>126.1508</v>
+        <v>146.1091</v>
       </c>
       <c r="E25" t="n">
-        <v>196.5939</v>
+        <v>204.8022</v>
       </c>
       <c r="F25" t="n">
-        <v>-70.44370000000001</v>
+        <v>-58.6925</v>
       </c>
       <c r="G25" t="n">
         <v>83.90819999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>-46.61199999999999</v>
+        <v>-46.61199999999998</v>
       </c>
       <c r="I25" t="n">
         <v>130.5195</v>
       </c>
       <c r="J25" t="n">
-        <v>384.1476</v>
+        <v>384.1476000000001</v>
       </c>
       <c r="K25" t="n">
         <v>192.9138</v>
@@ -2392,7 +2392,7 @@
         <v>-239.5257</v>
       </c>
       <c r="O25" t="n">
-        <v>-60.7137</v>
+        <v>-60.71370000000001</v>
       </c>
       <c r="P25" t="n">
         <v>14.8231</v>
@@ -2404,16 +2404,16 @@
         <v>402.0728</v>
       </c>
       <c r="S25" t="n">
-        <v>-26.7058</v>
+        <v>-6.747</v>
       </c>
       <c r="T25" t="n">
-        <v>-14.2522</v>
+        <v>-6.045599999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-12.4522</v>
+        <v>-0.7003999999999994</v>
       </c>
       <c r="V25" t="n">
-        <v>54.12520000000003</v>
+        <v>54.12519999999999</v>
       </c>
       <c r="W25" t="n">
         <v>213.9496</v>
